--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bfd7ebc1d5351f40/Documents/Processing/DearData100/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4301CC13-CAA8-4A9B-A0AD-D6DE0A0CBC92}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{438FAB89-B12B-44C6-81A7-E4F0A175B2BC}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5BDAE3-238F-4C0A-B4AB-9501E37C8513}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
   <si>
     <t>DATE</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>reading</t>
+  </si>
+  <si>
+    <t>deliveroo</t>
   </si>
 </sst>
 </file>
@@ -611,9 +614,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}" name="pickups" displayName="pickups" ref="A1:C26" totalsRowShown="0">
-  <autoFilter ref="A1:C26" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}" name="pickups" displayName="pickups" ref="A1:C30" totalsRowShown="0">
+  <autoFilter ref="A1:C30" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E4AC545B-D30E-4169-908F-3002877B03BF}" name="DATE" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{3E63D35E-30C3-4DF9-AEAA-7718D0F290E7}" name="TIME" dataDxfId="0"/>
@@ -940,7 +947,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D69329-82D4-4761-9A56-5144FEA16702}">
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1233,6 +1240,50 @@
         <v>12</v>
       </c>
     </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B27" s="2">
+        <v>0.37777777777777777</v>
+      </c>
+      <c r="C27" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B28" s="2">
+        <v>0.47291666666666665</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B29" s="2">
+        <v>0.56527777777777777</v>
+      </c>
+      <c r="C29" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0.71319444444444446</v>
+      </c>
+      <c r="C30" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bfd7ebc1d5351f40/Documents/Processing/DearData100/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{438FAB89-B12B-44C6-81A7-E4F0A175B2BC}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60411AD3-B331-46C7-8994-50B41A934472}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5BDAE3-238F-4C0A-B4AB-9501E37C8513}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="15">
   <si>
     <t>DATE</t>
   </si>
@@ -62,6 +62,9 @@
   </si>
   <si>
     <t>deliveroo</t>
+  </si>
+  <si>
+    <t>safari</t>
   </si>
 </sst>
 </file>
@@ -619,8 +622,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}" name="pickups" displayName="pickups" ref="A1:C30" totalsRowShown="0">
-  <autoFilter ref="A1:C30" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}" name="pickups" displayName="pickups" ref="A1:C100" totalsRowShown="0">
+  <autoFilter ref="A1:C100" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E4AC545B-D30E-4169-908F-3002877B03BF}" name="DATE" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{3E63D35E-30C3-4DF9-AEAA-7718D0F290E7}" name="TIME" dataDxfId="0"/>
@@ -947,7 +950,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D69329-82D4-4761-9A56-5144FEA16702}">
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -1275,14 +1278,478 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="B30" s="2">
-        <v>0.71319444444444446</v>
+        <v>0.35416666666666669</v>
       </c>
       <c r="C30" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0.37847222222222221</v>
+      </c>
+      <c r="C31" t="s">
         <v>4</v>
       </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B32" s="2">
+        <v>0.41736111111111113</v>
+      </c>
+      <c r="C32" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B33" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C33" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B34" s="2">
+        <v>0.58750000000000002</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B35" s="2">
+        <v>0.68958333333333333</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0.83125000000000004</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="C37" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B38" s="2">
+        <v>0.33541666666666664</v>
+      </c>
+      <c r="C38" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B39" s="2">
+        <v>0.43680555555555556</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B40" s="2">
+        <v>0.45416666666666666</v>
+      </c>
+      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B41" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0.58680555555555558</v>
+      </c>
+      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0.9194444444444444</v>
+      </c>
+      <c r="C43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B44" s="2">
+        <v>0.39652777777777776</v>
+      </c>
+      <c r="C44" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B45" s="2">
+        <v>0.40277777777777779</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B46" s="2">
+        <v>0.56597222222222221</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B47" s="2">
+        <v>0.65694444444444444</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0.7416666666666667</v>
+      </c>
+      <c r="C48" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B50" s="2">
+        <v>0.77986111111111112</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B51" s="2">
+        <v>0.88402777777777775</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B52" s="2">
+        <v>0.90625</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B53" s="2">
+        <v>0.91527777777777775</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0.36527777777777776</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0.44513888888888886</v>
+      </c>
+      <c r="C55" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B56" s="2">
+        <v>0.49722222222222223</v>
+      </c>
+      <c r="C56" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B57" s="2"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="B58" s="2"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="1"/>
+      <c r="B59" s="2"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="2"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="B61" s="2"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="B62" s="2"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="1"/>
+      <c r="B63" s="2"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="2"/>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="B65" s="2"/>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="B66" s="2"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="B67" s="2"/>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="1"/>
+      <c r="B68" s="2"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="2"/>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="2"/>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="1"/>
+      <c r="B71" s="2"/>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="1"/>
+      <c r="B72" s="2"/>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="B73" s="2"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="B74" s="2"/>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+      <c r="B75" s="2"/>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="1"/>
+      <c r="B76" s="2"/>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="B77" s="2"/>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="1"/>
+      <c r="B78" s="2"/>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="1"/>
+      <c r="B79" s="2"/>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+      <c r="B80" s="2"/>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="1"/>
+      <c r="B81" s="2"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="1"/>
+      <c r="B82" s="2"/>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+      <c r="B83" s="2"/>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="1"/>
+      <c r="B84" s="2"/>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="1"/>
+      <c r="B85" s="2"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="1"/>
+      <c r="B86" s="2"/>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="1"/>
+      <c r="B87" s="2"/>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="1"/>
+      <c r="B88" s="2"/>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="1"/>
+      <c r="B89" s="2"/>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="1"/>
+      <c r="B90" s="2"/>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
+      <c r="B91" s="2"/>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+      <c r="B92" s="2"/>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="1"/>
+      <c r="B93" s="2"/>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
+      <c r="B94" s="2"/>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="B95" s="2"/>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="B96" s="2"/>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="1"/>
+      <c r="B97" s="2"/>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="1"/>
+      <c r="B98" s="2"/>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="1"/>
+      <c r="B99" s="2"/>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="1"/>
+      <c r="B100" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bfd7ebc1d5351f40/Documents/Processing/DearData100/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60411AD3-B331-46C7-8994-50B41A934472}"/>
+  <xr:revisionPtr revIDLastSave="168" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41F361FA-CAD5-4968-AE02-0C10FD7C5C6C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5BDAE3-238F-4C0A-B4AB-9501E37C8513}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="16">
   <si>
     <t>DATE</t>
   </si>
@@ -65,6 +65,9 @@
   </si>
   <si>
     <t>safari</t>
+  </si>
+  <si>
+    <t>minecraft</t>
   </si>
 </sst>
 </file>
@@ -1577,161 +1580,362 @@
       <c r="A57" s="1">
         <v>46320</v>
       </c>
-      <c r="B57" s="2"/>
+      <c r="B57" s="2">
+        <v>0.5541666666666667</v>
+      </c>
+      <c r="C57" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="2"/>
+      <c r="A58" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B58" s="2">
+        <v>0.55972222222222223</v>
+      </c>
+      <c r="C58" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="B59" s="2"/>
+      <c r="A59" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B59" s="2">
+        <v>0.59930555555555554</v>
+      </c>
+      <c r="C59" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="B60" s="2"/>
+      <c r="A60" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0.65069444444444446</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-      <c r="B61" s="2"/>
+      <c r="A61" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0.77152777777777781</v>
+      </c>
+      <c r="C61" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="B62" s="2"/>
+      <c r="A62" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B62" s="2">
+        <v>0.91388888888888886</v>
+      </c>
+      <c r="C62" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="2"/>
+      <c r="A63" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B63" s="2">
+        <v>0.3125</v>
+      </c>
+      <c r="C63" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="2"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="2"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="B66" s="2"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-      <c r="B67" s="2"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="B68" s="2"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="2"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="2"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="B71" s="2"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="B72" s="2"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="B73" s="2"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-      <c r="B74" s="2"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
-      <c r="B75" s="2"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="1"/>
-      <c r="B76" s="2"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="1"/>
-      <c r="B77" s="2"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="2"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
-      <c r="B79" s="2"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="2"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="B81" s="2"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="B82" s="2"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="1"/>
-      <c r="B83" s="2"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="1"/>
-      <c r="B84" s="2"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
-      <c r="B85" s="2"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B64" s="2">
+        <v>0.33611111111111114</v>
+      </c>
+      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B65" s="2">
+        <v>0.35833333333333334</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B66" s="2">
+        <v>0.3840277777777778</v>
+      </c>
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B67" s="2">
+        <v>0.42569444444444443</v>
+      </c>
+      <c r="C67" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B68" s="2">
+        <v>0.61250000000000004</v>
+      </c>
+      <c r="C68" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B69" s="2">
+        <v>0.64375000000000004</v>
+      </c>
+      <c r="C69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B70" s="2">
+        <v>0.81388888888888888</v>
+      </c>
+      <c r="C70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B71" s="2">
+        <v>0.8979166666666667</v>
+      </c>
+      <c r="C71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B72" s="2">
+        <v>0.92291666666666672</v>
+      </c>
+      <c r="C72" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B73" s="2">
+        <v>0.28819444444444442</v>
+      </c>
+      <c r="C73" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B74" s="2">
+        <v>0.2951388888888889</v>
+      </c>
+      <c r="C74" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B75" s="2">
+        <v>0.32013888888888886</v>
+      </c>
+      <c r="C75" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B76" s="2">
+        <v>0.32777777777777778</v>
+      </c>
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="2">
+        <v>0.33611111111111114</v>
+      </c>
+      <c r="C77" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B78" s="2">
+        <v>0.34375</v>
+      </c>
+      <c r="C78" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B79" s="2">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="C79" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B80" s="2">
+        <v>0.46805555555555556</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B81" s="2">
+        <v>0.8256944444444444</v>
+      </c>
+      <c r="C81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B82" s="2">
+        <v>0.82777777777777772</v>
+      </c>
+      <c r="C82" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B83" s="2">
+        <v>0.85138888888888886</v>
+      </c>
+      <c r="C83" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B84" s="2">
+        <v>0.85347222222222219</v>
+      </c>
+      <c r="C84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B85" s="2">
+        <v>0.89097222222222228</v>
+      </c>
+      <c r="C85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="2"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="2"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="2"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="2"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="2"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="2"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="2"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="2"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="2"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="2"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="2"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bfd7ebc1d5351f40/Documents/Processing/DearData100/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="168" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41F361FA-CAD5-4968-AE02-0C10FD7C5C6C}"/>
+  <xr:revisionPtr revIDLastSave="199" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73447039-FA40-41E6-B9BB-E40436CF68C7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5BDAE3-238F-4C0A-B4AB-9501E37C8513}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C5BDAE3-238F-4C0A-B4AB-9501E37C8513}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="18">
   <si>
     <t>DATE</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>minecraft</t>
+  </si>
+  <si>
+    <t>messages</t>
+  </si>
+  <si>
+    <t>roblox</t>
   </si>
 </sst>
 </file>
@@ -954,13 +960,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D69329-82D4-4761-9A56-5144FEA16702}">
   <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -971,7 +977,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46312</v>
       </c>
@@ -982,7 +988,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46312</v>
       </c>
@@ -993,7 +999,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46312</v>
       </c>
@@ -1004,7 +1010,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46312</v>
       </c>
@@ -1015,7 +1021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46312</v>
       </c>
@@ -1026,7 +1032,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46312</v>
       </c>
@@ -1037,7 +1043,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46312</v>
       </c>
@@ -1048,7 +1054,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46313</v>
       </c>
@@ -1059,7 +1065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46313</v>
       </c>
@@ -1070,7 +1076,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46313</v>
       </c>
@@ -1081,7 +1087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>46313</v>
       </c>
@@ -1092,7 +1098,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>46313</v>
       </c>
@@ -1103,7 +1109,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>46313</v>
       </c>
@@ -1114,7 +1120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>46314</v>
       </c>
@@ -1125,7 +1131,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>46314</v>
       </c>
@@ -1136,7 +1142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>46314</v>
       </c>
@@ -1147,7 +1153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>46314</v>
       </c>
@@ -1158,7 +1164,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>46314</v>
       </c>
@@ -1169,7 +1175,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>46314</v>
       </c>
@@ -1180,7 +1186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>46315</v>
       </c>
@@ -1191,7 +1197,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>46315</v>
       </c>
@@ -1202,7 +1208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>46315</v>
       </c>
@@ -1213,7 +1219,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>46315</v>
       </c>
@@ -1224,7 +1230,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>46315</v>
       </c>
@@ -1235,7 +1241,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46315</v>
       </c>
@@ -1246,7 +1252,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46316</v>
       </c>
@@ -1257,7 +1263,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46316</v>
       </c>
@@ -1268,7 +1274,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46316</v>
       </c>
@@ -1279,7 +1285,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>46317</v>
       </c>
@@ -1290,7 +1296,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>46317</v>
       </c>
@@ -1301,7 +1307,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>46317</v>
       </c>
@@ -1312,7 +1318,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>46317</v>
       </c>
@@ -1323,7 +1329,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>46317</v>
       </c>
@@ -1334,7 +1340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>46317</v>
       </c>
@@ -1345,7 +1351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>46317</v>
       </c>
@@ -1356,7 +1362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>46317</v>
       </c>
@@ -1367,7 +1373,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>46318</v>
       </c>
@@ -1378,7 +1384,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>46318</v>
       </c>
@@ -1389,7 +1395,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>46318</v>
       </c>
@@ -1400,7 +1406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>46318</v>
       </c>
@@ -1411,7 +1417,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>46318</v>
       </c>
@@ -1422,7 +1428,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>46318</v>
       </c>
@@ -1433,7 +1439,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>46319</v>
       </c>
@@ -1444,7 +1450,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>46319</v>
       </c>
@@ -1455,7 +1461,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>46319</v>
       </c>
@@ -1466,7 +1472,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46319</v>
       </c>
@@ -1477,7 +1483,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46319</v>
       </c>
@@ -1488,7 +1494,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>46319</v>
       </c>
@@ -1499,7 +1505,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>46319</v>
       </c>
@@ -1510,7 +1516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>46319</v>
       </c>
@@ -1521,7 +1527,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>46319</v>
       </c>
@@ -1532,7 +1538,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>46319</v>
       </c>
@@ -1543,7 +1549,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46320</v>
       </c>
@@ -1554,7 +1560,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46320</v>
       </c>
@@ -1565,7 +1571,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46320</v>
       </c>
@@ -1576,7 +1582,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46320</v>
       </c>
@@ -1587,7 +1593,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>46320</v>
       </c>
@@ -1598,7 +1604,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>46320</v>
       </c>
@@ -1609,7 +1615,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>46320</v>
       </c>
@@ -1620,7 +1626,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>46320</v>
       </c>
@@ -1631,7 +1637,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>46320</v>
       </c>
@@ -1642,7 +1648,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>46321</v>
       </c>
@@ -1653,7 +1659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>46321</v>
       </c>
@@ -1664,7 +1670,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>46321</v>
       </c>
@@ -1675,7 +1681,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>46321</v>
       </c>
@@ -1686,7 +1692,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>46321</v>
       </c>
@@ -1697,7 +1703,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>46321</v>
       </c>
@@ -1708,7 +1714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>46321</v>
       </c>
@@ -1719,7 +1725,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>46321</v>
       </c>
@@ -1730,7 +1736,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>46321</v>
       </c>
@@ -1741,7 +1747,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>46321</v>
       </c>
@@ -1752,7 +1758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>46322</v>
       </c>
@@ -1763,7 +1769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>46322</v>
       </c>
@@ -1774,7 +1780,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>46322</v>
       </c>
@@ -1785,7 +1791,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>46322</v>
       </c>
@@ -1796,7 +1802,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>46322</v>
       </c>
@@ -1807,7 +1813,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>46322</v>
       </c>
@@ -1818,7 +1824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>46322</v>
       </c>
@@ -1829,7 +1835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>46322</v>
       </c>
@@ -1840,7 +1846,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>46322</v>
       </c>
@@ -1851,7 +1857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46322</v>
       </c>
@@ -1862,7 +1868,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46322</v>
       </c>
@@ -1873,7 +1879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46322</v>
       </c>
@@ -1884,7 +1890,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46322</v>
       </c>
@@ -1895,63 +1901,154 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="1"/>
-      <c r="B86" s="2"/>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-      <c r="B87" s="2"/>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="1"/>
-      <c r="B88" s="2"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-      <c r="B89" s="2"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-      <c r="B90" s="2"/>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="1"/>
-      <c r="B91" s="2"/>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-      <c r="B92" s="2"/>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-      <c r="B93" s="2"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="2"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="B95" s="2"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="1"/>
-      <c r="B96" s="2"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="1"/>
-      <c r="B97" s="2"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="1"/>
-      <c r="B98" s="2"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B86" s="2">
+        <v>0.92291666666666672</v>
+      </c>
+      <c r="C86" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B87" s="2">
+        <v>0.28055555555555556</v>
+      </c>
+      <c r="C87" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B88" s="2">
+        <v>0.44861111111111113</v>
+      </c>
+      <c r="C88" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B89" s="2">
+        <v>0.51736111111111116</v>
+      </c>
+      <c r="C89" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B90" s="2">
+        <v>0.52708333333333335</v>
+      </c>
+      <c r="C90" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B91" s="2">
+        <v>0.53472222222222221</v>
+      </c>
+      <c r="C91" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B92" s="2">
+        <v>0.54305555555555551</v>
+      </c>
+      <c r="C92" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A93" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B93" s="2">
+        <v>0.55069444444444449</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B94" s="2">
+        <v>0.56180555555555556</v>
+      </c>
+      <c r="C94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B95" s="2">
+        <v>0.57152777777777775</v>
+      </c>
+      <c r="C95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B96" s="2">
+        <v>0.5756944444444444</v>
+      </c>
+      <c r="C96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B97" s="2">
+        <v>0.58263888888888893</v>
+      </c>
+      <c r="C97" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B98" s="2">
+        <v>0.62430555555555556</v>
+      </c>
+      <c r="C98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="2"/>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="2"/>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bfd7ebc1d5351f40/Documents/Processing/DearData100/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="199" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73447039-FA40-41E6-B9BB-E40436CF68C7}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="8_{0A2D2040-7C1E-486A-A811-92823D1DEB5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7ED5DCE-DF6D-4229-B37C-D7ED71687EA7}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{3C5BDAE3-238F-4C0A-B4AB-9501E37C8513}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3C5BDAE3-238F-4C0A-B4AB-9501E37C8513}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="19">
   <si>
     <t>DATE</t>
   </si>
@@ -74,6 +74,9 @@
   </si>
   <si>
     <t>roblox</t>
+  </si>
+  <si>
+    <t>clash royal</t>
   </si>
 </sst>
 </file>
@@ -626,13 +629,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}" name="pickups" displayName="pickups" ref="A1:C100" totalsRowShown="0">
-  <autoFilter ref="A1:C100" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}" name="pickups" displayName="pickups" ref="A1:C104" totalsRowShown="0">
+  <autoFilter ref="A1:C104" xr:uid="{16F08334-34FB-4DB2-ADB4-6C42E4C09BFE}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{E4AC545B-D30E-4169-908F-3002877B03BF}" name="DATE" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{3E63D35E-30C3-4DF9-AEAA-7718D0F290E7}" name="TIME" dataDxfId="0"/>
@@ -959,14 +958,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82D69329-82D4-4761-9A56-5144FEA16702}">
-  <dimension ref="A1:C100"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:C104"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -977,7 +976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46312</v>
       </c>
@@ -988,7 +987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>46312</v>
       </c>
@@ -999,7 +998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>46312</v>
       </c>
@@ -1010,7 +1009,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>46312</v>
       </c>
@@ -1021,7 +1020,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>46312</v>
       </c>
@@ -1032,7 +1031,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>46312</v>
       </c>
@@ -1043,7 +1042,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>46312</v>
       </c>
@@ -1054,7 +1053,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>46313</v>
       </c>
@@ -1065,7 +1064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>46313</v>
       </c>
@@ -1076,7 +1075,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46313</v>
       </c>
@@ -1087,7 +1086,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46313</v>
       </c>
@@ -1098,7 +1097,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46313</v>
       </c>
@@ -1109,7 +1108,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>46313</v>
       </c>
@@ -1120,7 +1119,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>46314</v>
       </c>
@@ -1131,7 +1130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>46314</v>
       </c>
@@ -1142,7 +1141,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>46314</v>
       </c>
@@ -1153,7 +1152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>46314</v>
       </c>
@@ -1164,7 +1163,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>46314</v>
       </c>
@@ -1175,7 +1174,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>46314</v>
       </c>
@@ -1186,7 +1185,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>46315</v>
       </c>
@@ -1197,7 +1196,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>46315</v>
       </c>
@@ -1208,7 +1207,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>46315</v>
       </c>
@@ -1219,7 +1218,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>46315</v>
       </c>
@@ -1230,7 +1229,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>46315</v>
       </c>
@@ -1241,7 +1240,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>46315</v>
       </c>
@@ -1252,7 +1251,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>46316</v>
       </c>
@@ -1263,7 +1262,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>46316</v>
       </c>
@@ -1274,7 +1273,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>46316</v>
       </c>
@@ -1285,7 +1284,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>46317</v>
       </c>
@@ -1296,7 +1295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>46317</v>
       </c>
@@ -1307,7 +1306,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>46317</v>
       </c>
@@ -1318,7 +1317,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>46317</v>
       </c>
@@ -1329,7 +1328,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>46317</v>
       </c>
@@ -1340,7 +1339,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>46317</v>
       </c>
@@ -1351,7 +1350,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>46317</v>
       </c>
@@ -1362,7 +1361,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>46317</v>
       </c>
@@ -1373,7 +1372,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>46318</v>
       </c>
@@ -1384,7 +1383,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>46318</v>
       </c>
@@ -1395,7 +1394,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>46318</v>
       </c>
@@ -1406,7 +1405,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>46318</v>
       </c>
@@ -1417,7 +1416,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>46318</v>
       </c>
@@ -1428,7 +1427,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>46318</v>
       </c>
@@ -1439,7 +1438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>46319</v>
       </c>
@@ -1450,7 +1449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>46319</v>
       </c>
@@ -1461,7 +1460,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>46319</v>
       </c>
@@ -1472,7 +1471,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>46319</v>
       </c>
@@ -1483,7 +1482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>46319</v>
       </c>
@@ -1494,7 +1493,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>46319</v>
       </c>
@@ -1505,7 +1504,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>46319</v>
       </c>
@@ -1516,7 +1515,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>46319</v>
       </c>
@@ -1527,7 +1526,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>46319</v>
       </c>
@@ -1538,7 +1537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>46319</v>
       </c>
@@ -1549,7 +1548,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>46320</v>
       </c>
@@ -1560,7 +1559,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46320</v>
       </c>
@@ -1571,7 +1570,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>46320</v>
       </c>
@@ -1582,7 +1581,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>46320</v>
       </c>
@@ -1593,7 +1592,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>46320</v>
       </c>
@@ -1604,7 +1603,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>46320</v>
       </c>
@@ -1615,7 +1614,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>46320</v>
       </c>
@@ -1626,7 +1625,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>46320</v>
       </c>
@@ -1637,7 +1636,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>46320</v>
       </c>
@@ -1648,7 +1647,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>46321</v>
       </c>
@@ -1659,7 +1658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>46321</v>
       </c>
@@ -1670,7 +1669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>46321</v>
       </c>
@@ -1681,7 +1680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>46321</v>
       </c>
@@ -1692,7 +1691,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>46321</v>
       </c>
@@ -1703,7 +1702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>46321</v>
       </c>
@@ -1714,7 +1713,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>46321</v>
       </c>
@@ -1725,7 +1724,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>46321</v>
       </c>
@@ -1736,7 +1735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>46321</v>
       </c>
@@ -1747,7 +1746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>46321</v>
       </c>
@@ -1758,7 +1757,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>46322</v>
       </c>
@@ -1769,7 +1768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>46322</v>
       </c>
@@ -1780,7 +1779,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>46322</v>
       </c>
@@ -1791,7 +1790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>46322</v>
       </c>
@@ -1802,7 +1801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>46322</v>
       </c>
@@ -1813,7 +1812,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>46322</v>
       </c>
@@ -1824,7 +1823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>46322</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>46322</v>
       </c>
@@ -1846,7 +1845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>46322</v>
       </c>
@@ -1857,7 +1856,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>46322</v>
       </c>
@@ -1868,7 +1867,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>46322</v>
       </c>
@@ -1879,7 +1878,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>46322</v>
       </c>
@@ -1890,7 +1889,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>46322</v>
       </c>
@@ -1901,7 +1900,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>46322</v>
       </c>
@@ -1912,7 +1911,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>46323</v>
       </c>
@@ -1923,7 +1922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>46323</v>
       </c>
@@ -1934,7 +1933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>46323</v>
       </c>
@@ -1945,7 +1944,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>46323</v>
       </c>
@@ -1956,7 +1955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>46323</v>
       </c>
@@ -1967,7 +1966,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>46323</v>
       </c>
@@ -1978,7 +1977,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>46323</v>
       </c>
@@ -1989,7 +1988,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>46323</v>
       </c>
@@ -2000,7 +1999,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>46323</v>
       </c>
@@ -2011,7 +2010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>46323</v>
       </c>
@@ -2022,7 +2021,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>46323</v>
       </c>
@@ -2033,7 +2032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>46323</v>
       </c>
@@ -2044,13 +2043,71 @@
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A99" s="1"/>
-      <c r="B99" s="2"/>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A100" s="1"/>
-      <c r="B100" s="2"/>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B99" s="2">
+        <v>0.6743055555555556</v>
+      </c>
+      <c r="C99" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B100" s="2">
+        <v>0.68125000000000002</v>
+      </c>
+      <c r="C100" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B101" s="2">
+        <v>0.7319444444444444</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B102" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="C102" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B103" s="2">
+        <v>0.90069444444444446</v>
+      </c>
+      <c r="C103" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B104" s="2">
+        <v>0.91041666666666665</v>
+      </c>
+      <c r="C104" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
